--- a/DataTables/Datas/dialog.xlsx
+++ b/DataTables/Datas/dialog.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,6 +457,11 @@
           <t>speakerid2</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>##备注</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">

--- a/DataTables/Datas/dialog.xlsx
+++ b/DataTables/Datas/dialog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\Hippo-s-Epic\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12C93080-F0A4-46A1-AC29-60AF86199787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3A34322-025C-45AD-9327-D93AEDFC1CC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="42">
   <si>
     <t>##var</t>
   </si>
@@ -146,7 +146,17 @@
     <t>关于这个小镇</t>
   </si>
   <si>
-    <t>一拳打在他脸上！|教练这下惨了</t>
+    <t>一拳打在他脸上！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1|2|1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当对话类型为选项时：
+1代表普通对话
+2代表动作对话</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -190,8 +200,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -497,9 +510,11 @@
   <dimension ref="A1:I21"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
+    <col min="2" max="2" width="26.625" customWidth="1"/>
+    <col min="3" max="3" width="21.25" customWidth="1"/>
     <col min="4" max="4" width="19.75" customWidth="1"/>
     <col min="5" max="5" width="20.375" customWidth="1"/>
-    <col min="6" max="6" width="31.25" customWidth="1"/>
+    <col min="6" max="6" width="37" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.15">
@@ -557,15 +572,18 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A3" t="s">
+    <row r="3" spans="1:9" s="1" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>16</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.15">
@@ -620,6 +638,9 @@
       </c>
       <c r="D6" t="s">
         <v>24</v>
+      </c>
+      <c r="E6" t="s">
+        <v>40</v>
       </c>
       <c r="G6">
         <v>1</v>

--- a/DataTables/Datas/dialog.xlsx
+++ b/DataTables/Datas/dialog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\Hippo-s-Epic\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3A34322-025C-45AD-9327-D93AEDFC1CC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7A4D69F-4513-4A0C-B365-CA5D4874F865}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -72,10 +72,6 @@
     <t>##</t>
   </si>
   <si>
-    <t>1.普通对话
-2.带选项的普通对话</t>
-  </si>
-  <si>
     <t>每个对话类型的不同参数代表不同的作用
 用于解决条件选项问题</t>
   </si>
@@ -99,9 +95,6 @@
   </si>
   <si>
     <t>说话人2</t>
-  </si>
-  <si>
-    <t>3|4|5</t>
   </si>
   <si>
     <t>我是来患上一种病叫查尔斯顿狂&lt;br&gt;热，然后一直跳舞跳到屎尿横流为止</t>
@@ -157,6 +150,16 @@
     <t>当对话类型为选项时：
 1代表普通对话
 2代表动作对话</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>章节数*1000000+对话数*1000+语句数
+1.普通对话
+2.带选项的普通对话</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001003|1001004|1001005</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -180,12 +183,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -200,10 +209,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -507,406 +525,411 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="2" max="2" width="26.625" customWidth="1"/>
-    <col min="3" max="3" width="21.25" customWidth="1"/>
-    <col min="4" max="4" width="19.75" customWidth="1"/>
-    <col min="5" max="5" width="20.375" customWidth="1"/>
-    <col min="6" max="6" width="37" customWidth="1"/>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="26.625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.25" style="1" customWidth="1"/>
+    <col min="4" max="4" width="31.125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="37" style="2" customWidth="1"/>
+    <col min="7" max="7" width="28" style="1" customWidth="1"/>
+    <col min="8" max="8" width="27.875" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:9" s="1" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:9" s="2" customFormat="1" ht="66.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="E3" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="B4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="B5" s="1">
+        <v>1001001</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1001002</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1</v>
+      </c>
+      <c r="H5" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="B6" s="1">
+        <v>1001002</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="E6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="B7" s="1">
+        <v>1001003</v>
+      </c>
+      <c r="C7" s="1">
+        <v>1</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1001002</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="G7" s="1">
+        <v>1</v>
+      </c>
+      <c r="H7" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="B8" s="1">
+        <v>1001004</v>
+      </c>
+      <c r="C8" s="1">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1</v>
+      </c>
+      <c r="H8" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="B9" s="1">
+        <v>1001005</v>
+      </c>
+      <c r="C9" s="1">
+        <v>1</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1001002</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E6" t="s">
-        <v>40</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="B7">
-        <v>3</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="G9" s="1">
+        <v>1</v>
+      </c>
+      <c r="H9" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B11" s="3">
+        <v>100</v>
+      </c>
+      <c r="C11" s="3">
+        <v>1</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="B8">
-        <v>4</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="F8" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-      <c r="H8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="B9">
-        <v>5</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>2</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="F11" s="4"/>
+      <c r="G11" s="3">
+        <v>1</v>
+      </c>
+      <c r="H11" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="B12" s="1">
+        <v>101</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1">
+        <v>1</v>
+      </c>
+      <c r="H12" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="B13" s="1">
+        <v>200</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-      <c r="H9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="B10">
-        <v>100</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="G13" s="1">
+        <v>1</v>
+      </c>
+      <c r="H13" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="B14" s="1">
+        <v>201</v>
+      </c>
+      <c r="C14" s="1">
+        <v>1</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-      <c r="H10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="B11">
-        <v>101</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="H11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="B12">
-        <v>200</v>
-      </c>
-      <c r="C12">
-        <v>2</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="F14" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-      <c r="H12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="B13">
-        <v>201</v>
-      </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="G14" s="1">
+        <v>1</v>
+      </c>
+      <c r="H14" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="B15" s="1">
+        <v>202</v>
+      </c>
+      <c r="C15" s="1">
+        <v>1</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F15" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-      <c r="H13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="B14">
-        <v>202</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="G15" s="1">
+        <v>1</v>
+      </c>
+      <c r="H15" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="B16" s="1">
+        <v>203</v>
+      </c>
+      <c r="C16" s="1">
+        <v>1</v>
+      </c>
+      <c r="G16" s="1">
+        <v>1</v>
+      </c>
+      <c r="H16" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.15">
+      <c r="B17" s="1">
+        <v>300</v>
+      </c>
+      <c r="C17" s="1">
+        <v>2</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G17" s="1">
+        <v>1</v>
+      </c>
+      <c r="H17" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.15">
+      <c r="B18" s="1">
+        <v>301</v>
+      </c>
+      <c r="C18" s="1">
+        <v>2</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-      <c r="H14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="B15">
-        <v>203</v>
-      </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-      <c r="H15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="B16">
-        <v>300</v>
-      </c>
-      <c r="C16">
-        <v>2</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="F18" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-      <c r="H16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B17">
-        <v>301</v>
-      </c>
-      <c r="C17">
-        <v>2</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="G18" s="1">
+        <v>1</v>
+      </c>
+      <c r="H18" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
+      <c r="B19" s="1">
+        <v>302</v>
+      </c>
+      <c r="C19" s="1">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G19" s="1">
+        <v>1</v>
+      </c>
+      <c r="H19" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.15">
+      <c r="B20" s="1">
+        <v>303</v>
+      </c>
+      <c r="C20" s="1">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-      <c r="H17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B18">
-        <v>302</v>
-      </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="F18" t="s">
+      <c r="G20" s="1">
+        <v>1</v>
+      </c>
+      <c r="H20" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
+      <c r="B21" s="1">
+        <v>304</v>
+      </c>
+      <c r="C21" s="1">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-      <c r="H18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B19">
-        <v>303</v>
-      </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="F19" t="s">
-        <v>37</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-      <c r="H19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B20">
-        <v>304</v>
-      </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="F20" t="s">
-        <v>38</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-      <c r="H20">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B21">
+      <c r="G21" s="1">
+        <v>1</v>
+      </c>
+      <c r="H21" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
+      <c r="B22" s="1">
         <v>400</v>
       </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-      <c r="G21">
-        <v>1</v>
-      </c>
-      <c r="H21">
+      <c r="C22" s="1">
+        <v>1</v>
+      </c>
+      <c r="G22" s="1">
+        <v>1</v>
+      </c>
+      <c r="H22" s="1">
         <v>2</v>
       </c>
     </row>

--- a/DataTables/Datas/dialog.xlsx
+++ b/DataTables/Datas/dialog.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="9" customWidth="1" style="1" min="1" max="1"/>
@@ -1015,7 +1015,6 @@
       <c r="C22" t="n">
         <v>1</v>
       </c>
-      <c r="D22" t="inlineStr"/>
       <c r="G22" t="n">
         <v>1</v>
       </c>
@@ -1024,6 +1023,17 @@
       </c>
       <c r="I22" t="n">
         <v>1001</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>600</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/Datas/dialog.xlsx
+++ b/DataTables/Datas/dialog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\Hippo-s-Epic\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0CB1B67-6960-4CA8-94FC-E8856FF373CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D81B9CEE-7509-439B-A9ED-B5E4295DDCBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -136,15 +136,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>暂时还没有发现，顺便问下选手们的牙还有痊愈的可能吗</t>
+    <t>我可以报名上场吗，我想成为一个伟大的人</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>我在拳王更衣室里找到了这个报道</t>
+    <t>递给教练拳王更衣室找到的报道</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>我可以报名上场吗，我想成为一个伟大的人</t>
+    <t>呃，呃，其实我暂时还没有什么发现。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -803,7 +803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10" s="3" customFormat="1" ht="27" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B13" s="3">
         <v>1003003</v>
       </c>
@@ -814,7 +814,7 @@
         <v>1003006</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G13" s="3">
         <v>1</v>
@@ -854,7 +854,7 @@
         <v>1</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G15" s="3">
         <v>1</v>

--- a/DataTables/Datas/dialog.xlsx
+++ b/DataTables/Datas/dialog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\Hippo-s-Epic\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D81B9CEE-7509-439B-A9ED-B5E4295DDCBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16152063-58BB-4275-9BA1-C8664B13A7FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/DataTables/Datas/dialog.xlsx
+++ b/DataTables/Datas/dialog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\Hippo-s-Epic\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16152063-58BB-4275-9BA1-C8664B13A7FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79611B75-B6D7-4EA7-8F12-A71EC0A423D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -511,7 +511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" style="1" customWidth="1"/>
@@ -810,9 +810,6 @@
       <c r="C13" s="3">
         <v>1</v>
       </c>
-      <c r="D13" s="3">
-        <v>1003006</v>
-      </c>
       <c r="F13" s="4" t="s">
         <v>36</v>
       </c>
@@ -863,24 +860,6 @@
         <v>2</v>
       </c>
       <c r="I15" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="3">
-        <v>1003006</v>
-      </c>
-      <c r="C16" s="3">
-        <v>1</v>
-      </c>
-      <c r="F16" s="4"/>
-      <c r="G16" s="3">
-        <v>1</v>
-      </c>
-      <c r="H16" s="3">
-        <v>2</v>
-      </c>
-      <c r="I16" s="5">
         <v>0</v>
       </c>
     </row>

--- a/DataTables/Datas/dialog.xlsx
+++ b/DataTables/Datas/dialog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\Hippo-s-Epic\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C0F1C8F-9138-4853-B4D8-0942636B3EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B243607E-D19B-48A9-928C-493B175D778C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -953,15 +953,27 @@
       </c>
     </row>
     <row r="17" spans="2:10" s="5" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
+      <c r="B17" s="9">
+        <v>1004002</v>
+      </c>
+      <c r="C17" s="9">
+        <v>2</v>
+      </c>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
+      <c r="G17" s="5">
+        <v>1</v>
+      </c>
+      <c r="H17" s="5">
+        <v>4</v>
+      </c>
+      <c r="I17" s="9">
+        <v>0</v>
+      </c>
+      <c r="J17" s="9">
+        <v>0</v>
+      </c>
     </row>
     <row r="18" spans="2:10" s="5" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B18" s="9"/>
